--- a/data/trans_orig/ESTUDIOS-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2007</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1029816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1031723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1313158</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1315113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2344901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2346835</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1691442</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1693413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1585712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1587673</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3279119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3281086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>549403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>551408</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>474393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>476412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1025806</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1027820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>504486</t>
+          <t>509292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>593968</t>
+          <t>600239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>438292</t>
+          <t>438952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>520395</t>
+          <t>516263</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>973294</t>
+          <t>966748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1091586</t>
+          <t>1094736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1635903</t>
+          <t>1627685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1751126</t>
+          <t>1750356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1529325</t>
+          <t>1530722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1646395</t>
+          <t>1646221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3190490</t>
+          <t>3194336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3359739</t>
+          <t>3362410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>973795</t>
+          <t>983225</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1084056</t>
+          <t>1088008</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1254028</t>
+          <t>1252523</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1366719</t>
+          <t>1367276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2267662</t>
+          <t>2259779</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2423993</t>
+          <t>2412654</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2012</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>972584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>974643</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1335738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1337797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2310380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2312440</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1961926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1963957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1755740</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1757803</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3719713</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3721760</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>456499</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>458631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>937692</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>939813</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>435808</t>
+          <t>441643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>520932</t>
+          <t>524800</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>418653</t>
+          <t>416935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>497333</t>
+          <t>497515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>879508</t>
+          <t>883662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1000252</t>
+          <t>1003061</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1905733</t>
+          <t>1904778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2025050</t>
+          <t>2023077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1696621</t>
+          <t>1699465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1815997</t>
+          <t>1818182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3635073</t>
+          <t>3635571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3803877</t>
+          <t>3806724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>925115</t>
+          <t>919538</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1030407</t>
+          <t>1034254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1275324</t>
+          <t>1276796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1390487</t>
+          <t>1394574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2236082</t>
+          <t>2228586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2391923</t>
+          <t>2393811</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2016</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>752449</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>754347</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>992521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>994660</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1746977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1749007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2074343</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2076385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1986300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1988300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4062663</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4064685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>544794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>546886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>547139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>549140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1093980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1096027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>503587</t>
+          <t>505598</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>592799</t>
+          <t>592706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>504970</t>
+          <t>503545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>597590</t>
+          <t>590770</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1037197</t>
+          <t>1043913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1157595</t>
+          <t>1163837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2024470</t>
+          <t>2019681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2136866</t>
+          <t>2137122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1929646</t>
+          <t>1927529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2051783</t>
+          <t>2048841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3973205</t>
+          <t>3989228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4138121</t>
+          <t>4149508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>708414</t>
+          <t>701210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>801609</t>
+          <t>799716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>940730</t>
+          <t>939460</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1055023</t>
+          <t>1053606</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1677152</t>
+          <t>1675399</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1822310</t>
+          <t>1818983</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nivel de estudios en 2023</t>
+          <t>Población según el nivel de estudios más alto finalizado en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513509</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269295</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236352</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4526380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305597</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>501443</t>
+          <t>506288</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>718854</t>
+          <t>714052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>540195</t>
+          <t>534566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>721328</t>
+          <t>724014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1124701</t>
+          <t>1142504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1416665</t>
+          <t>1412003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2184617</t>
+          <t>2180364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2548430</t>
+          <t>2546506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2118079</t>
+          <t>2123130</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2504404</t>
+          <t>2513248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,47 +8429,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>4913</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4528150</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>4342465</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4870359</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>63,73%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>68,54%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>4528150</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>4338019</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4883446</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>63,73%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>400712</t>
+          <t>400690</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>570666</t>
+          <t>574038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>612161</t>
+          <t>616359</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>826788</t>
+          <t>820730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1092163</t>
+          <t>1099221</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1366081</t>
+          <t>1372437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ESTUDIOS-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ESTUDIOS-Estudios-trans_orig.xlsx
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>509292</t>
+          <t>510725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>600239</t>
+          <t>598849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>438952</t>
+          <t>439315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>516263</t>
+          <t>520038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>966748</t>
+          <t>972865</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1094736</t>
+          <t>1087365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1627685</t>
+          <t>1634483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1750356</t>
+          <t>1749045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1530722</t>
+          <t>1526643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1646221</t>
+          <t>1645457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3194336</t>
+          <t>3202345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3362410</t>
+          <t>3360901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>983225</t>
+          <t>981453</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1088008</t>
+          <t>1084128</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1252523</t>
+          <t>1259040</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1367276</t>
+          <t>1371631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2259779</t>
+          <t>2270234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2412654</t>
+          <t>2424643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>441643</t>
+          <t>440170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>524800</t>
+          <t>520178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>416935</t>
+          <t>419779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>497515</t>
+          <t>500177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>883662</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1003061</t>
+          <t>1002585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1904778</t>
+          <t>1903962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2023077</t>
+          <t>2025145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1699465</t>
+          <t>1696572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1818182</t>
+          <t>1822178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3635571</t>
+          <t>3632840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3806724</t>
+          <t>3810155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>919538</t>
+          <t>918790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1034254</t>
+          <t>1028475</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1276796</t>
+          <t>1272847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1394574</t>
+          <t>1397965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2228586</t>
+          <t>2232955</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2393811</t>
+          <t>2397915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>505598</t>
+          <t>502448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>592706</t>
+          <t>591218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>503545</t>
+          <t>507561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>590770</t>
+          <t>591602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1043913</t>
+          <t>1036004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1163837</t>
+          <t>1166070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2019681</t>
+          <t>2011761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2137122</t>
+          <t>2133059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1927529</t>
+          <t>1927905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2048841</t>
+          <t>2050732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3989228</t>
+          <t>3980850</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4149508</t>
+          <t>4147983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>701210</t>
+          <t>704061</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>799716</t>
+          <t>805964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>939460</t>
+          <t>939649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1053606</t>
+          <t>1052867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1675399</t>
+          <t>1678934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1818983</t>
+          <t>1823928</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>506288</t>
+          <t>657160</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>714052</t>
+          <t>764457</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>534566</t>
+          <t>693606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>724014</t>
+          <t>780144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1142504</t>
+          <t>1381434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1412003</t>
+          <t>1517799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2180364</t>
+          <t>2169774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2546506</t>
+          <t>2296031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2123130</t>
+          <t>2119928</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2513248</t>
+          <t>2227481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401958</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4342465</t>
+          <t>4321951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4870359</t>
+          <t>4480650</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>400690</t>
+          <t>535058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>574038</t>
+          <t>623416</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>616359</t>
+          <t>777850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>820730</t>
+          <t>863139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1099221</t>
+          <t>1341891</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1372437</t>
+          <t>1457889</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
